--- a/output/Data and Chart Outputs/miso_gas_burn_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_gas_burn_daily.xlsx
@@ -22,8 +22,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -292,6 +293,7 @@
           </tx>
           <overlay val="0"/>
         </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -432,6 +434,7 @@
           </tx>
           <overlay val="0"/>
         </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1016,7 +1019,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1059,7 +1061,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -1088,7 +1089,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
@@ -1103,7 +1103,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
@@ -1125,7 +1124,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
@@ -1210,7 +1208,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B2" t="n">
@@ -1218,7 +1216,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B3" t="n">
@@ -1226,7 +1224,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B4" t="n">
@@ -1234,7 +1232,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B5" t="n">
@@ -1242,7 +1240,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B6" t="n">
@@ -1250,7 +1248,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B7" t="n">
@@ -1258,7 +1256,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B8" t="n">
@@ -1266,7 +1264,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B9" t="n">
@@ -1274,7 +1272,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B10" t="n">
@@ -1282,7 +1280,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B11" t="n">
@@ -1290,7 +1288,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B12" t="n">
@@ -1298,7 +1296,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B13" t="n">
@@ -1306,7 +1304,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -1317,7 +1315,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B15" t="n">
@@ -1328,7 +1326,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B16" t="n">
@@ -1339,7 +1337,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B17" t="n">
@@ -1350,7 +1348,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B18" t="n">
@@ -1361,7 +1359,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B19" t="n">
@@ -1372,7 +1370,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -1383,7 +1381,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B21" t="n">
@@ -1394,7 +1392,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B22" t="n">
@@ -1405,7 +1403,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B23" t="n">
@@ -1416,7 +1414,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B24" t="n">
@@ -1427,7 +1425,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B25" t="n">
@@ -1438,7 +1436,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B26" t="n">
@@ -1449,7 +1447,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B27" t="n">
@@ -1460,7 +1458,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B28" t="n">
@@ -1471,7 +1469,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B29" t="n">
@@ -1482,7 +1480,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B30" t="n">
@@ -1493,7 +1491,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B31" t="n">
@@ -1504,7 +1502,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B32" t="n">
@@ -1515,7 +1513,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B33" t="n">
@@ -1526,7 +1524,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B34" t="n">
@@ -1537,7 +1535,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B35" t="n">
@@ -1548,7 +1546,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B36" t="n">
@@ -1559,7 +1557,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B37" t="n">
@@ -1570,7 +1568,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B38" t="n">
@@ -1581,7 +1579,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B39" t="n">
@@ -1592,7 +1590,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B40" t="n">
@@ -1603,7 +1601,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B41" t="n">
@@ -1614,7 +1612,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B42" t="n">
@@ -1625,7 +1623,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B43" t="n">
@@ -1636,7 +1634,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B44" t="n">
@@ -1682,7 +1680,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B2" t="n">
@@ -1695,7 +1693,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45659</v>
       </c>
       <c r="B3" t="n">
@@ -1703,7 +1701,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45660</v>
       </c>
       <c r="B4" t="n">
@@ -1711,7 +1709,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45661</v>
       </c>
       <c r="B5" t="n">
@@ -1719,7 +1717,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45662</v>
       </c>
       <c r="B6" t="n">
@@ -1727,7 +1725,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45663</v>
       </c>
       <c r="B7" t="n">
@@ -1735,7 +1733,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45664</v>
       </c>
       <c r="B8" t="n">
@@ -1743,7 +1741,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45665</v>
       </c>
       <c r="B9" t="n">
@@ -1751,7 +1749,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45666</v>
       </c>
       <c r="B10" t="n">
@@ -1759,7 +1757,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45667</v>
       </c>
       <c r="B11" t="n">
@@ -1767,7 +1765,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45668</v>
       </c>
       <c r="B12" t="n">
@@ -1775,7 +1773,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45669</v>
       </c>
       <c r="B13" t="n">
@@ -1783,7 +1781,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45670</v>
       </c>
       <c r="B14" t="n">
@@ -1791,7 +1789,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45671</v>
       </c>
       <c r="B15" t="n">
@@ -1799,7 +1797,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45672</v>
       </c>
       <c r="B16" t="n">
@@ -1807,7 +1805,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45673</v>
       </c>
       <c r="B17" t="n">
@@ -1815,7 +1813,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45674</v>
       </c>
       <c r="B18" t="n">
@@ -1823,7 +1821,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45675</v>
       </c>
       <c r="B19" t="n">
@@ -1831,7 +1829,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45676</v>
       </c>
       <c r="B20" t="n">
@@ -1839,7 +1837,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B21" t="n">
@@ -1847,7 +1845,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45678</v>
       </c>
       <c r="B22" t="n">
@@ -1855,7 +1853,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45679</v>
       </c>
       <c r="B23" t="n">
@@ -1863,7 +1861,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45680</v>
       </c>
       <c r="B24" t="n">
@@ -1871,7 +1869,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45681</v>
       </c>
       <c r="B25" t="n">
@@ -1879,7 +1877,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>45682</v>
       </c>
       <c r="B26" t="n">
@@ -1887,7 +1885,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>45683</v>
       </c>
       <c r="B27" t="n">
@@ -1895,7 +1893,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>45684</v>
       </c>
       <c r="B28" t="n">
@@ -1903,7 +1901,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45685</v>
       </c>
       <c r="B29" t="n">
@@ -1911,7 +1909,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45686</v>
       </c>
       <c r="B30" t="n">
@@ -1919,7 +1917,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45687</v>
       </c>
       <c r="B31" t="n">
@@ -1927,7 +1925,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45688</v>
       </c>
       <c r="B32" t="n">
@@ -1935,7 +1933,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1941,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45690</v>
       </c>
       <c r="B34" t="n">
@@ -1951,7 +1949,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45691</v>
       </c>
       <c r="B35" t="n">
@@ -1959,7 +1957,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45692</v>
       </c>
       <c r="B36" t="n">
@@ -1967,7 +1965,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45693</v>
       </c>
       <c r="B37" t="n">
@@ -1975,7 +1973,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45694</v>
       </c>
       <c r="B38" t="n">
@@ -1983,7 +1981,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45695</v>
       </c>
       <c r="B39" t="n">
@@ -1991,7 +1989,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45696</v>
       </c>
       <c r="B40" t="n">
@@ -1999,7 +1997,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45697</v>
       </c>
       <c r="B41" t="n">
@@ -2007,7 +2005,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45698</v>
       </c>
       <c r="B42" t="n">
@@ -2015,7 +2013,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B43" t="n">
@@ -2023,7 +2021,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45700</v>
       </c>
       <c r="B44" t="n">
@@ -2031,7 +2029,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45701</v>
       </c>
       <c r="B45" t="n">
@@ -2039,7 +2037,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45702</v>
       </c>
       <c r="B46" t="n">
@@ -2047,7 +2045,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45703</v>
       </c>
       <c r="B47" t="n">
@@ -2055,7 +2053,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45704</v>
       </c>
       <c r="B48" t="n">
@@ -2063,7 +2061,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45705</v>
       </c>
       <c r="B49" t="n">
@@ -2071,7 +2069,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45706</v>
       </c>
       <c r="B50" t="n">
@@ -2079,7 +2077,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45707</v>
       </c>
       <c r="B51" t="n">
@@ -2087,7 +2085,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45708</v>
       </c>
       <c r="B52" t="n">
@@ -2095,7 +2093,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="B53" t="n">
@@ -2103,7 +2101,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45710</v>
       </c>
       <c r="B54" t="n">
@@ -2111,7 +2109,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45711</v>
       </c>
       <c r="B55" t="n">
@@ -2119,7 +2117,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45712</v>
       </c>
       <c r="B56" t="n">
@@ -2127,7 +2125,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45713</v>
       </c>
       <c r="B57" t="n">
@@ -2135,7 +2133,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45714</v>
       </c>
       <c r="B58" t="n">
@@ -2143,7 +2141,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45715</v>
       </c>
       <c r="B59" t="n">
@@ -2151,7 +2149,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45716</v>
       </c>
       <c r="B60" t="n">
@@ -2159,7 +2157,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B61" t="n">
@@ -2172,7 +2170,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="B62" t="n">
@@ -2180,7 +2178,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>45719</v>
       </c>
       <c r="B63" t="n">
@@ -2188,7 +2186,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>45720</v>
       </c>
       <c r="B64" t="n">
@@ -2196,7 +2194,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>45721</v>
       </c>
       <c r="B65" t="n">
@@ -2204,7 +2202,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>45722</v>
       </c>
       <c r="B66" t="n">
@@ -2212,7 +2210,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>45723</v>
       </c>
       <c r="B67" t="n">
@@ -2220,7 +2218,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>45724</v>
       </c>
       <c r="B68" t="n">
@@ -2228,7 +2226,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>45725</v>
       </c>
       <c r="B69" t="n">
@@ -2236,7 +2234,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>45726</v>
       </c>
       <c r="B70" t="n">
@@ -2244,7 +2242,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>45727</v>
       </c>
       <c r="B71" t="n">
@@ -2252,7 +2250,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>45728</v>
       </c>
       <c r="B72" t="n">
@@ -2260,7 +2258,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>45729</v>
       </c>
       <c r="B73" t="n">
@@ -2268,7 +2266,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>45730</v>
       </c>
       <c r="B74" t="n">
@@ -2276,7 +2274,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>45731</v>
       </c>
       <c r="B75" t="n">
@@ -2284,7 +2282,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>45732</v>
       </c>
       <c r="B76" t="n">
@@ -2292,7 +2290,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B77" t="n">
@@ -2300,7 +2298,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>45734</v>
       </c>
       <c r="B78" t="n">
@@ -2308,7 +2306,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>45735</v>
       </c>
       <c r="B79" t="n">
@@ -2316,7 +2314,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>45736</v>
       </c>
       <c r="B80" t="n">
@@ -2324,7 +2322,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>45737</v>
       </c>
       <c r="B81" t="n">
@@ -2332,7 +2330,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>45738</v>
       </c>
       <c r="B82" t="n">
@@ -2340,7 +2338,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>45739</v>
       </c>
       <c r="B83" t="n">
@@ -2348,7 +2346,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>45740</v>
       </c>
       <c r="B84" t="n">
@@ -2356,7 +2354,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>45741</v>
       </c>
       <c r="B85" t="n">
@@ -2364,7 +2362,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>45742</v>
       </c>
       <c r="B86" t="n">
@@ -2372,7 +2370,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>45743</v>
       </c>
       <c r="B87" t="n">
@@ -2380,7 +2378,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>45744</v>
       </c>
       <c r="B88" t="n">
@@ -2388,7 +2386,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>45745</v>
       </c>
       <c r="B89" t="n">
@@ -2396,7 +2394,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>45746</v>
       </c>
       <c r="B90" t="n">
@@ -2404,7 +2402,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B91" t="n">
@@ -2412,7 +2410,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B92" t="n">
@@ -2420,7 +2418,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>45749</v>
       </c>
       <c r="B93" t="n">
@@ -2428,7 +2426,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>45750</v>
       </c>
       <c r="B94" t="n">
@@ -2436,7 +2434,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>45751</v>
       </c>
       <c r="B95" t="n">
@@ -2444,7 +2442,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>45752</v>
       </c>
       <c r="B96" t="n">
@@ -2452,7 +2450,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="3" t="n">
         <v>45753</v>
       </c>
       <c r="B97" t="n">
@@ -2460,7 +2458,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="B98" t="n">
@@ -2468,7 +2466,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="3" t="n">
         <v>45755</v>
       </c>
       <c r="B99" t="n">
@@ -2476,7 +2474,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="3" t="n">
         <v>45756</v>
       </c>
       <c r="B100" t="n">
@@ -2484,7 +2482,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="3" t="n">
         <v>45757</v>
       </c>
       <c r="B101" t="n">
@@ -2492,7 +2490,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="3" t="n">
         <v>45758</v>
       </c>
       <c r="B102" t="n">
@@ -2500,7 +2498,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="3" t="n">
         <v>45759</v>
       </c>
       <c r="B103" t="n">
@@ -2508,7 +2506,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="3" t="n">
         <v>45760</v>
       </c>
       <c r="B104" t="n">
@@ -2516,7 +2514,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="3" t="n">
         <v>45761</v>
       </c>
       <c r="B105" t="n">
@@ -2524,7 +2522,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="3" t="n">
         <v>45762</v>
       </c>
       <c r="B106" t="n">
@@ -2532,7 +2530,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="3" t="n">
         <v>45763</v>
       </c>
       <c r="B107" t="n">
@@ -2540,7 +2538,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="3" t="n">
         <v>45764</v>
       </c>
       <c r="B108" t="n">
@@ -2548,7 +2546,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="3" t="n">
         <v>45765</v>
       </c>
       <c r="B109" t="n">
@@ -2556,7 +2554,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="3" t="n">
         <v>45766</v>
       </c>
       <c r="B110" t="n">
@@ -2564,7 +2562,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="3" t="n">
         <v>45767</v>
       </c>
       <c r="B111" t="n">
@@ -2572,7 +2570,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="3" t="n">
         <v>45768</v>
       </c>
       <c r="B112" t="n">
@@ -2580,7 +2578,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="3" t="n">
         <v>45769</v>
       </c>
       <c r="B113" t="n">
@@ -2588,7 +2586,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="3" t="n">
         <v>45770</v>
       </c>
       <c r="B114" t="n">
@@ -2596,7 +2594,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="3" t="n">
         <v>45771</v>
       </c>
       <c r="B115" t="n">
@@ -2604,7 +2602,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="3" t="n">
         <v>45772</v>
       </c>
       <c r="B116" t="n">
@@ -2612,7 +2610,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="3" t="n">
         <v>45773</v>
       </c>
       <c r="B117" t="n">
@@ -2620,7 +2618,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="3" t="n">
         <v>45774</v>
       </c>
       <c r="B118" t="n">
@@ -2628,7 +2626,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="3" t="n">
         <v>45775</v>
       </c>
       <c r="B119" t="n">
@@ -2636,7 +2634,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="3" t="n">
         <v>45776</v>
       </c>
       <c r="B120" t="n">
@@ -2644,7 +2642,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="3" t="n">
         <v>45777</v>
       </c>
       <c r="B121" t="n">
@@ -2652,7 +2650,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B122" t="n">
@@ -2665,7 +2663,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="3" t="n">
         <v>45779</v>
       </c>
       <c r="B123" t="n">
@@ -2673,7 +2671,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="3" t="n">
         <v>45780</v>
       </c>
       <c r="B124" t="n">
@@ -2681,7 +2679,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="3" t="n">
         <v>45781</v>
       </c>
       <c r="B125" t="n">
@@ -2689,7 +2687,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="3" t="n">
         <v>45782</v>
       </c>
       <c r="B126" t="n">
@@ -2697,7 +2695,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="3" t="n">
         <v>45783</v>
       </c>
       <c r="B127" t="n">
@@ -2705,7 +2703,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="3" t="n">
         <v>45784</v>
       </c>
       <c r="B128" t="n">
@@ -2713,7 +2711,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="3" t="n">
         <v>45785</v>
       </c>
       <c r="B129" t="n">
@@ -2721,7 +2719,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="3" t="n">
         <v>45786</v>
       </c>
       <c r="B130" t="n">
@@ -2729,7 +2727,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="3" t="n">
         <v>45787</v>
       </c>
       <c r="B131" t="n">
@@ -2737,7 +2735,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="3" t="n">
         <v>45788</v>
       </c>
       <c r="B132" t="n">
@@ -2745,7 +2743,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="3" t="n">
         <v>45789</v>
       </c>
       <c r="B133" t="n">
@@ -2753,7 +2751,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="3" t="n">
         <v>45790</v>
       </c>
       <c r="B134" t="n">
@@ -2761,7 +2759,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="3" t="n">
         <v>45791</v>
       </c>
       <c r="B135" t="n">
@@ -2769,7 +2767,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="3" t="n">
         <v>45792</v>
       </c>
       <c r="B136" t="n">
@@ -2777,7 +2775,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="3" t="n">
         <v>45793</v>
       </c>
       <c r="B137" t="n">
@@ -2785,7 +2783,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="3" t="n">
         <v>45794</v>
       </c>
       <c r="B138" t="n">
@@ -2793,7 +2791,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="3" t="n">
         <v>45795</v>
       </c>
       <c r="B139" t="n">
@@ -2801,7 +2799,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="3" t="n">
         <v>45796</v>
       </c>
       <c r="B140" t="n">
@@ -2809,7 +2807,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="3" t="n">
         <v>45797</v>
       </c>
       <c r="B141" t="n">
@@ -2817,7 +2815,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="3" t="n">
         <v>45798</v>
       </c>
       <c r="B142" t="n">
@@ -2825,7 +2823,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="3" t="n">
         <v>45799</v>
       </c>
       <c r="B143" t="n">
@@ -2833,7 +2831,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="3" t="n">
         <v>45800</v>
       </c>
       <c r="B144" t="n">
@@ -2841,7 +2839,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="3" t="n">
         <v>45801</v>
       </c>
       <c r="B145" t="n">
@@ -2849,7 +2847,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="3" t="n">
         <v>45802</v>
       </c>
       <c r="B146" t="n">
@@ -2857,7 +2855,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="3" t="n">
         <v>45803</v>
       </c>
       <c r="B147" t="n">
@@ -2865,7 +2863,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="3" t="n">
         <v>45804</v>
       </c>
       <c r="B148" t="n">
@@ -2873,7 +2871,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="3" t="n">
         <v>45805</v>
       </c>
       <c r="B149" t="n">
@@ -2881,7 +2879,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="3" t="n">
         <v>45806</v>
       </c>
       <c r="B150" t="n">
@@ -2889,7 +2887,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="3" t="n">
         <v>45807</v>
       </c>
       <c r="B151" t="n">
@@ -2897,7 +2895,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="3" t="n">
         <v>45808</v>
       </c>
       <c r="B152" t="n">
@@ -2905,7 +2903,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B153" t="n">
@@ -2913,7 +2911,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="3" t="n">
         <v>45810</v>
       </c>
       <c r="B154" t="n">
@@ -2921,7 +2919,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="3" t="n">
         <v>45811</v>
       </c>
       <c r="B155" t="n">
@@ -2929,7 +2927,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="3" t="n">
         <v>45812</v>
       </c>
       <c r="B156" t="n">
@@ -2937,7 +2935,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="3" t="n">
         <v>45813</v>
       </c>
       <c r="B157" t="n">
@@ -2945,7 +2943,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="3" t="n">
         <v>45814</v>
       </c>
       <c r="B158" t="n">
@@ -2953,7 +2951,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="3" t="n">
         <v>45815</v>
       </c>
       <c r="B159" t="n">
@@ -2961,7 +2959,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="B160" t="n">
@@ -2969,7 +2967,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="3" t="n">
         <v>45817</v>
       </c>
       <c r="B161" t="n">
@@ -2977,7 +2975,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="3" t="n">
         <v>45818</v>
       </c>
       <c r="B162" t="n">
@@ -2985,7 +2983,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="3" t="n">
         <v>45819</v>
       </c>
       <c r="B163" t="n">
@@ -2993,7 +2991,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="3" t="n">
         <v>45820</v>
       </c>
       <c r="B164" t="n">
@@ -3001,7 +2999,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="3" t="n">
         <v>45821</v>
       </c>
       <c r="B165" t="n">
@@ -3009,7 +3007,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="3" t="n">
         <v>45822</v>
       </c>
       <c r="B166" t="n">
@@ -3017,7 +3015,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="3" t="n">
         <v>45823</v>
       </c>
       <c r="B167" t="n">
@@ -3025,7 +3023,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="3" t="n">
         <v>45824</v>
       </c>
       <c r="B168" t="n">
@@ -3033,7 +3031,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="3" t="n">
         <v>45825</v>
       </c>
       <c r="B169" t="n">
@@ -3041,7 +3039,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="3" t="n">
         <v>45826</v>
       </c>
       <c r="B170" t="n">
@@ -3049,7 +3047,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="3" t="n">
         <v>45827</v>
       </c>
       <c r="B171" t="n">
@@ -3057,7 +3055,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="3" t="n">
         <v>45828</v>
       </c>
       <c r="B172" t="n">
@@ -3065,7 +3063,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="3" t="n">
         <v>45829</v>
       </c>
       <c r="B173" t="n">
@@ -3073,7 +3071,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="3" t="n">
         <v>45830</v>
       </c>
       <c r="B174" t="n">
@@ -3081,7 +3079,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="3" t="n">
         <v>45831</v>
       </c>
       <c r="B175" t="n">
@@ -3089,7 +3087,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="3" t="n">
         <v>45832</v>
       </c>
       <c r="B176" t="n">
@@ -3097,7 +3095,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="3" t="n">
         <v>45833</v>
       </c>
       <c r="B177" t="n">
@@ -3105,7 +3103,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="3" t="n">
         <v>45834</v>
       </c>
       <c r="B178" t="n">
@@ -3113,7 +3111,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="3" t="n">
         <v>45835</v>
       </c>
       <c r="B179" t="n">
@@ -3121,7 +3119,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="B180" t="n">
@@ -3129,7 +3127,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="3" t="n">
         <v>45837</v>
       </c>
       <c r="B181" t="n">
@@ -3137,7 +3135,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="3" t="n">
         <v>45838</v>
       </c>
       <c r="B182" t="n">
@@ -3145,7 +3143,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B183" t="n">
@@ -3158,7 +3156,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="3" t="n">
         <v>45840</v>
       </c>
       <c r="B184" t="n">
@@ -3166,7 +3164,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="3" t="n">
         <v>45841</v>
       </c>
       <c r="B185" t="n">
@@ -3174,7 +3172,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="3" t="n">
         <v>45842</v>
       </c>
       <c r="B186" t="n">
@@ -3182,7 +3180,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="3" t="n">
         <v>45843</v>
       </c>
       <c r="B187" t="n">
@@ -3190,7 +3188,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="3" t="n">
         <v>45844</v>
       </c>
       <c r="B188" t="n">
@@ -3198,7 +3196,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="3" t="n">
         <v>45845</v>
       </c>
       <c r="B189" t="n">
@@ -3206,7 +3204,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="3" t="n">
         <v>45846</v>
       </c>
       <c r="B190" t="n">
@@ -3214,7 +3212,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="3" t="n">
         <v>45847</v>
       </c>
       <c r="B191" t="n">
@@ -3222,7 +3220,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="3" t="n">
         <v>45848</v>
       </c>
       <c r="B192" t="n">
@@ -3230,7 +3228,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="3" t="n">
         <v>45849</v>
       </c>
       <c r="B193" t="n">
@@ -3238,7 +3236,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="3" t="n">
         <v>45850</v>
       </c>
       <c r="B194" t="n">
@@ -3246,7 +3244,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="3" t="n">
         <v>45851</v>
       </c>
       <c r="B195" t="n">
@@ -3254,7 +3252,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="3" t="n">
         <v>45852</v>
       </c>
       <c r="B196" t="n">
@@ -3262,7 +3260,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="3" t="n">
         <v>45853</v>
       </c>
       <c r="B197" t="n">
@@ -3270,7 +3268,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="3" t="n">
         <v>45854</v>
       </c>
       <c r="B198" t="n">
@@ -3278,7 +3276,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="3" t="n">
         <v>45855</v>
       </c>
       <c r="B199" t="n">
@@ -3286,7 +3284,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="3" t="n">
         <v>45856</v>
       </c>
       <c r="B200" t="n">
@@ -3294,7 +3292,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="3" t="n">
         <v>45857</v>
       </c>
       <c r="B201" t="n">
@@ -3302,7 +3300,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="3" t="n">
         <v>45858</v>
       </c>
       <c r="B202" t="n">
@@ -3310,7 +3308,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="3" t="n">
         <v>45859</v>
       </c>
       <c r="B203" t="n">
@@ -3318,7 +3316,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="B204" t="n">
@@ -3326,7 +3324,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="3" t="n">
         <v>45861</v>
       </c>
       <c r="B205" t="n">
@@ -3334,7 +3332,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="B206" t="n">
@@ -3342,7 +3340,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="3" t="n">
         <v>45863</v>
       </c>
       <c r="B207" t="n">
@@ -3350,7 +3348,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="3" t="n">
         <v>45864</v>
       </c>
       <c r="B208" t="n">
@@ -3358,7 +3356,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="3" t="n">
         <v>45865</v>
       </c>
       <c r="B209" t="n">
@@ -3366,7 +3364,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="3" t="n">
         <v>45866</v>
       </c>
       <c r="B210" t="n">
@@ -3374,7 +3372,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="3" t="n">
         <v>45867</v>
       </c>
       <c r="B211" t="n">
@@ -3382,7 +3380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B212" t="n">
@@ -3390,7 +3388,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="3" t="n">
         <v>45869</v>
       </c>
       <c r="B213" t="n">
@@ -3398,7 +3396,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B214" t="n">
@@ -3406,7 +3404,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="3" t="n">
         <v>45871</v>
       </c>
       <c r="B215" t="n">
@@ -3414,7 +3412,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="3" t="n">
         <v>45872</v>
       </c>
       <c r="B216" t="n">
@@ -3422,7 +3420,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="3" t="n">
         <v>45873</v>
       </c>
       <c r="B217" t="n">
@@ -3430,7 +3428,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="3" t="n">
         <v>45874</v>
       </c>
       <c r="B218" t="n">
@@ -3438,7 +3436,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="3" t="n">
         <v>45875</v>
       </c>
       <c r="B219" t="n">
@@ -3446,7 +3444,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="3" t="n">
         <v>45876</v>
       </c>
       <c r="B220" t="n">
@@ -3454,7 +3452,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="3" t="n">
         <v>45877</v>
       </c>
       <c r="B221" t="n">
@@ -3462,7 +3460,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="3" t="n">
         <v>45878</v>
       </c>
       <c r="B222" t="n">
@@ -3470,7 +3468,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="3" t="n">
         <v>45879</v>
       </c>
       <c r="B223" t="n">
@@ -3478,7 +3476,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="3" t="n">
         <v>45880</v>
       </c>
       <c r="B224" t="n">
@@ -3486,7 +3484,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="3" t="n">
         <v>45881</v>
       </c>
       <c r="B225" t="n">
@@ -3494,7 +3492,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="3" t="n">
         <v>45882</v>
       </c>
       <c r="B226" t="n">
@@ -3502,7 +3500,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="3" t="n">
         <v>45883</v>
       </c>
       <c r="B227" t="n">
@@ -3510,7 +3508,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="3" t="n">
         <v>45884</v>
       </c>
       <c r="B228" t="n">
@@ -3518,7 +3516,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="3" t="n">
         <v>45885</v>
       </c>
       <c r="B229" t="n">
@@ -3526,7 +3524,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="3" t="n">
         <v>45886</v>
       </c>
       <c r="B230" t="n">
@@ -3534,7 +3532,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="3" t="n">
         <v>45887</v>
       </c>
       <c r="B231" t="n">
@@ -3542,7 +3540,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="3" t="n">
         <v>45888</v>
       </c>
       <c r="B232" t="n">
@@ -3550,7 +3548,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="3" t="n">
         <v>45889</v>
       </c>
       <c r="B233" t="n">
@@ -3558,7 +3556,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="3" t="n">
         <v>45890</v>
       </c>
       <c r="B234" t="n">
@@ -3566,7 +3564,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="3" t="n">
         <v>45891</v>
       </c>
       <c r="B235" t="n">
@@ -3574,7 +3572,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="3" t="n">
         <v>45892</v>
       </c>
       <c r="B236" t="n">
@@ -3582,7 +3580,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="3" t="n">
         <v>45893</v>
       </c>
       <c r="B237" t="n">
@@ -3590,7 +3588,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="3" t="n">
         <v>45894</v>
       </c>
       <c r="B238" t="n">
@@ -3598,7 +3596,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="3" t="n">
         <v>45895</v>
       </c>
       <c r="B239" t="n">
@@ -3606,7 +3604,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="3" t="n">
         <v>45896</v>
       </c>
       <c r="B240" t="n">
@@ -3614,7 +3612,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="3" t="n">
         <v>45897</v>
       </c>
       <c r="B241" t="n">
@@ -3622,7 +3620,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="3" t="n">
         <v>45898</v>
       </c>
       <c r="B242" t="n">
@@ -3630,7 +3628,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="3" t="n">
         <v>45899</v>
       </c>
       <c r="B243" t="n">
@@ -3638,7 +3636,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="3" t="n">
         <v>45900</v>
       </c>
       <c r="B244" t="n">
@@ -3646,7 +3644,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B245" t="n">
@@ -3659,7 +3657,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="B246" t="n">
@@ -3667,7 +3665,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="3" t="n">
         <v>45903</v>
       </c>
       <c r="B247" t="n">
@@ -3675,7 +3673,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="3" t="n">
         <v>45904</v>
       </c>
       <c r="B248" t="n">
@@ -3683,7 +3681,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="3" t="n">
         <v>45905</v>
       </c>
       <c r="B249" t="n">
@@ -3691,7 +3689,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="3" t="n">
         <v>45906</v>
       </c>
       <c r="B250" t="n">
@@ -3699,7 +3697,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="3" t="n">
         <v>45907</v>
       </c>
       <c r="B251" t="n">
@@ -3707,7 +3705,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="3" t="n">
         <v>45908</v>
       </c>
       <c r="B252" t="n">
@@ -3715,7 +3713,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="3" t="n">
         <v>45909</v>
       </c>
       <c r="B253" t="n">
@@ -3723,7 +3721,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="3" t="n">
         <v>45910</v>
       </c>
       <c r="B254" t="n">
@@ -3731,7 +3729,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="3" t="n">
         <v>45911</v>
       </c>
       <c r="B255" t="n">
@@ -3739,7 +3737,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="B256" t="n">
@@ -3747,7 +3745,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="3" t="n">
         <v>45913</v>
       </c>
       <c r="B257" t="n">
@@ -3755,7 +3753,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="3" t="n">
         <v>45914</v>
       </c>
       <c r="B258" t="n">
@@ -3763,7 +3761,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="3" t="n">
         <v>45915</v>
       </c>
       <c r="B259" t="n">
@@ -3771,7 +3769,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="3" t="n">
         <v>45916</v>
       </c>
       <c r="B260" t="n">
@@ -3779,7 +3777,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="B261" t="n">
@@ -3787,7 +3785,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="3" t="n">
         <v>45918</v>
       </c>
       <c r="B262" t="n">
@@ -3795,7 +3793,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B263" t="n">
@@ -3803,7 +3801,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="B264" t="n">
@@ -3811,7 +3809,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="3" t="n">
         <v>45921</v>
       </c>
       <c r="B265" t="n">
@@ -3819,7 +3817,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="3" t="n">
         <v>45922</v>
       </c>
       <c r="B266" t="n">
@@ -3827,7 +3825,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="3" t="n">
         <v>45923</v>
       </c>
       <c r="B267" t="n">
@@ -3835,7 +3833,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="3" t="n">
         <v>45924</v>
       </c>
       <c r="B268" t="n">
@@ -3843,7 +3841,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="B269" t="n">
@@ -3851,7 +3849,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="B270" t="n">
@@ -3859,7 +3857,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="B271" t="n">
@@ -3867,7 +3865,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="3" t="n">
         <v>45928</v>
       </c>
       <c r="B272" t="n">
@@ -3875,7 +3873,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="3" t="n">
         <v>45929</v>
       </c>
       <c r="B273" t="n">
@@ -3883,7 +3881,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="3" t="n">
         <v>45930</v>
       </c>
       <c r="B274" t="n">
@@ -3891,7 +3889,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B275" t="n">
@@ -3899,7 +3897,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="3" t="n">
         <v>45932</v>
       </c>
       <c r="B276" t="n">
@@ -3907,7 +3905,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="3" t="n">
         <v>45933</v>
       </c>
       <c r="B277" t="n">
@@ -3915,7 +3913,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="3" t="n">
         <v>45934</v>
       </c>
       <c r="B278" t="n">
@@ -3923,7 +3921,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="3" t="n">
         <v>45935</v>
       </c>
       <c r="B279" t="n">
@@ -3931,7 +3929,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="3" t="n">
         <v>45936</v>
       </c>
       <c r="B280" t="n">
@@ -3939,7 +3937,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="3" t="n">
         <v>45937</v>
       </c>
       <c r="B281" t="n">
@@ -3947,7 +3945,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="3" t="n">
         <v>45938</v>
       </c>
       <c r="B282" t="n">
@@ -3955,7 +3953,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="3" t="n">
         <v>45939</v>
       </c>
       <c r="B283" t="n">
@@ -3963,7 +3961,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="3" t="n">
         <v>45940</v>
       </c>
       <c r="B284" t="n">
@@ -3971,7 +3969,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="3" t="n">
         <v>45941</v>
       </c>
       <c r="B285" t="n">
@@ -3979,7 +3977,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="3" t="n">
         <v>45942</v>
       </c>
       <c r="B286" t="n">
@@ -3987,7 +3985,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="3" t="n">
         <v>45943</v>
       </c>
       <c r="B287" t="n">
@@ -3995,7 +3993,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="3" t="n">
         <v>45944</v>
       </c>
       <c r="B288" t="n">
@@ -4003,7 +4001,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="3" t="n">
         <v>45945</v>
       </c>
       <c r="B289" t="n">
@@ -4011,7 +4009,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="B290" t="n">
@@ -4019,7 +4017,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="B291" t="n">
@@ -4027,7 +4025,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="B292" t="n">
@@ -4035,7 +4033,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="3" t="n">
         <v>45949</v>
       </c>
       <c r="B293" t="n">
@@ -4043,7 +4041,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="3" t="n">
         <v>45950</v>
       </c>
       <c r="B294" t="n">
@@ -4051,7 +4049,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="B295" t="n">
@@ -4059,7 +4057,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="3" t="n">
         <v>45952</v>
       </c>
       <c r="B296" t="n">
@@ -4067,7 +4065,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="3" t="n">
         <v>45953</v>
       </c>
       <c r="B297" t="n">
@@ -4075,7 +4073,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="3" t="n">
         <v>45954</v>
       </c>
       <c r="B298" t="n">
@@ -4083,7 +4081,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="3" t="n">
         <v>45955</v>
       </c>
       <c r="B299" t="n">
@@ -4091,7 +4089,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="3" t="n">
         <v>45956</v>
       </c>
       <c r="B300" t="n">
@@ -4099,7 +4097,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="3" t="n">
         <v>45957</v>
       </c>
       <c r="B301" t="n">
@@ -4107,7 +4105,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="3" t="n">
         <v>45958</v>
       </c>
       <c r="B302" t="n">
@@ -4115,7 +4113,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B303" t="n">
@@ -4123,7 +4121,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="3" t="n">
         <v>45960</v>
       </c>
       <c r="B304" t="n">
@@ -4131,7 +4129,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="B305" t="n">
@@ -4139,7 +4137,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B306" t="n">
@@ -4152,7 +4150,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="3" t="n">
         <v>45963</v>
       </c>
       <c r="B307" t="n">
@@ -4160,7 +4158,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="3" t="n">
         <v>45964</v>
       </c>
       <c r="B308" t="n">
@@ -4168,7 +4166,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="3" t="n">
         <v>45965</v>
       </c>
       <c r="B309" t="n">
@@ -4176,7 +4174,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="3" t="n">
         <v>45966</v>
       </c>
       <c r="B310" t="n">
@@ -4184,7 +4182,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="3" t="n">
         <v>45967</v>
       </c>
       <c r="B311" t="n">
@@ -4192,7 +4190,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="3" t="n">
         <v>45968</v>
       </c>
       <c r="B312" t="n">
@@ -4200,7 +4198,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="3" t="n">
         <v>45969</v>
       </c>
       <c r="B313" t="n">
@@ -4208,7 +4206,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="3" t="n">
         <v>45970</v>
       </c>
       <c r="B314" t="n">
@@ -4216,7 +4214,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="3" t="n">
         <v>45971</v>
       </c>
       <c r="B315" t="n">
@@ -4224,7 +4222,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="3" t="n">
         <v>45972</v>
       </c>
       <c r="B316" t="n">
@@ -4232,7 +4230,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="3" t="n">
         <v>45973</v>
       </c>
       <c r="B317" t="n">
@@ -4240,7 +4238,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="3" t="n">
         <v>45974</v>
       </c>
       <c r="B318" t="n">
@@ -4248,7 +4246,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="3" t="n">
         <v>45975</v>
       </c>
       <c r="B319" t="n">
@@ -4256,7 +4254,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="3" t="n">
         <v>45976</v>
       </c>
       <c r="B320" t="n">
@@ -4264,7 +4262,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="3" t="n">
         <v>45977</v>
       </c>
       <c r="B321" t="n">
@@ -4272,7 +4270,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="3" t="n">
         <v>45978</v>
       </c>
       <c r="B322" t="n">
@@ -4280,7 +4278,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="3" t="n">
         <v>45979</v>
       </c>
       <c r="B323" t="n">
@@ -4288,7 +4286,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="3" t="n">
         <v>45980</v>
       </c>
       <c r="B324" t="n">
@@ -4296,7 +4294,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="3" t="n">
         <v>45981</v>
       </c>
       <c r="B325" t="n">
@@ -4304,7 +4302,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="3" t="n">
         <v>45982</v>
       </c>
       <c r="B326" t="n">
@@ -4312,7 +4310,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="3" t="n">
         <v>45983</v>
       </c>
       <c r="B327" t="n">
@@ -4320,7 +4318,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="3" t="n">
         <v>45984</v>
       </c>
       <c r="B328" t="n">
@@ -4328,7 +4326,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="3" t="n">
         <v>45985</v>
       </c>
       <c r="B329" t="n">
@@ -4336,7 +4334,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="3" t="n">
         <v>45986</v>
       </c>
       <c r="B330" t="n">
@@ -4344,7 +4342,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="3" t="n">
         <v>45987</v>
       </c>
       <c r="B331" t="n">
@@ -4352,7 +4350,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="3" t="n">
         <v>45988</v>
       </c>
       <c r="B332" t="n">
@@ -4360,7 +4358,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="3" t="n">
         <v>45989</v>
       </c>
       <c r="B333" t="n">
@@ -4368,7 +4366,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="3" t="n">
         <v>45990</v>
       </c>
       <c r="B334" t="n">
@@ -4376,7 +4374,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="3" t="n">
         <v>45991</v>
       </c>
       <c r="B335" t="n">
@@ -4384,7 +4382,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B336" t="n">
@@ -4392,7 +4390,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="3" t="n">
         <v>45993</v>
       </c>
       <c r="B337" t="n">
@@ -4400,7 +4398,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="3" t="n">
         <v>45994</v>
       </c>
       <c r="B338" t="n">
@@ -4408,7 +4406,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="B339" t="n">
@@ -4416,7 +4414,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="3" t="n">
         <v>45996</v>
       </c>
       <c r="B340" t="n">
@@ -4424,7 +4422,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="3" t="n">
         <v>45997</v>
       </c>
       <c r="B341" t="n">
@@ -4432,7 +4430,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="B342" t="n">
@@ -4440,7 +4438,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="3" t="n">
         <v>45999</v>
       </c>
       <c r="B343" t="n">
@@ -4448,7 +4446,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="B344" t="n">
@@ -4456,7 +4454,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="3" t="n">
         <v>46001</v>
       </c>
       <c r="B345" t="n">
@@ -4464,7 +4462,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="3" t="n">
         <v>46002</v>
       </c>
       <c r="B346" t="n">
@@ -4472,7 +4470,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="3" t="n">
         <v>46003</v>
       </c>
       <c r="B347" t="n">
@@ -4480,7 +4478,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="3" t="n">
         <v>46004</v>
       </c>
       <c r="B348" t="n">
@@ -4488,7 +4486,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="3" t="n">
         <v>46005</v>
       </c>
       <c r="B349" t="n">
@@ -4496,7 +4494,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="3" t="n">
         <v>46006</v>
       </c>
       <c r="B350" t="n">
@@ -4504,7 +4502,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="3" t="n">
         <v>46007</v>
       </c>
       <c r="B351" t="n">
@@ -4512,7 +4510,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="3" t="n">
         <v>46008</v>
       </c>
       <c r="B352" t="n">
@@ -4520,7 +4518,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="B353" t="n">
@@ -4528,7 +4526,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="3" t="n">
         <v>46010</v>
       </c>
       <c r="B354" t="n">
@@ -4536,7 +4534,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="3" t="n">
         <v>46011</v>
       </c>
       <c r="B355" t="n">
@@ -4544,7 +4542,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="3" t="n">
         <v>46012</v>
       </c>
       <c r="B356" t="n">
@@ -4552,7 +4550,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="3" t="n">
         <v>46013</v>
       </c>
       <c r="B357" t="n">
@@ -4560,7 +4558,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="3" t="n">
         <v>46014</v>
       </c>
       <c r="B358" t="n">
@@ -4568,7 +4566,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="3" t="n">
         <v>46015</v>
       </c>
       <c r="B359" t="n">
@@ -4576,7 +4574,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="3" t="n">
         <v>46016</v>
       </c>
       <c r="B360" t="n">
@@ -4584,7 +4582,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="3" t="n">
         <v>46017</v>
       </c>
       <c r="B361" t="n">
@@ -4592,7 +4590,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="3" t="n">
         <v>46018</v>
       </c>
       <c r="B362" t="n">
@@ -4600,7 +4598,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="3" t="n">
         <v>46019</v>
       </c>
       <c r="B363" t="n">
@@ -4608,7 +4606,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="3" t="n">
         <v>46020</v>
       </c>
       <c r="B364" t="n">
@@ -4616,7 +4614,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="3" t="n">
         <v>46021</v>
       </c>
       <c r="B365" t="n">
@@ -4624,7 +4622,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="3" t="n">
         <v>46022</v>
       </c>
       <c r="B366" t="n">
@@ -4632,7 +4630,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B367" t="n">
@@ -4645,7 +4643,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="3" t="n">
         <v>46024</v>
       </c>
       <c r="B368" t="n">
@@ -4653,7 +4651,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="3" t="n">
         <v>46025</v>
       </c>
       <c r="B369" t="n">
@@ -4661,7 +4659,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="3" t="n">
         <v>46026</v>
       </c>
       <c r="B370" t="n">
@@ -4669,7 +4667,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="3" t="n">
         <v>46027</v>
       </c>
       <c r="B371" t="n">
@@ -4677,7 +4675,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="B372" t="n">
@@ -4685,7 +4683,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="3" t="n">
         <v>46029</v>
       </c>
       <c r="B373" t="n">
@@ -4693,7 +4691,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="3" t="n">
         <v>46030</v>
       </c>
       <c r="B374" t="n">
@@ -4701,7 +4699,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="3" t="n">
         <v>46031</v>
       </c>
       <c r="B375" t="n">
@@ -4709,7 +4707,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="3" t="n">
         <v>46032</v>
       </c>
       <c r="B376" t="n">
@@ -4717,7 +4715,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="3" t="n">
         <v>46033</v>
       </c>
       <c r="B377" t="n">
@@ -4725,7 +4723,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="3" t="n">
         <v>46034</v>
       </c>
       <c r="B378" t="n">
@@ -4733,7 +4731,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="3" t="n">
         <v>46035</v>
       </c>
       <c r="B379" t="n">
@@ -4741,7 +4739,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="B380" t="n">
@@ -4749,7 +4747,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="B381" t="n">
@@ -4757,7 +4755,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="3" t="n">
         <v>46038</v>
       </c>
       <c r="B382" t="n">
@@ -4765,7 +4763,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="3" t="n">
         <v>46039</v>
       </c>
       <c r="B383" t="n">
@@ -4773,7 +4771,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="3" t="n">
         <v>46040</v>
       </c>
       <c r="B384" t="n">
@@ -4781,7 +4779,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="3" t="n">
         <v>46041</v>
       </c>
       <c r="B385" t="n">
@@ -4789,7 +4787,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="3" t="n">
         <v>46042</v>
       </c>
       <c r="B386" t="n">
@@ -4797,7 +4795,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="3" t="n">
         <v>46043</v>
       </c>
       <c r="B387" t="n">
@@ -4805,7 +4803,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="3" t="n">
         <v>46044</v>
       </c>
       <c r="B388" t="n">
@@ -4813,7 +4811,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="3" t="n">
         <v>46045</v>
       </c>
       <c r="B389" t="n">
@@ -4821,7 +4819,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="3" t="n">
         <v>46047</v>
       </c>
       <c r="B390" t="n">
@@ -4829,7 +4827,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="3" t="n">
         <v>46048</v>
       </c>
       <c r="B391" t="n">
@@ -4837,7 +4835,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="3" t="n">
         <v>46049</v>
       </c>
       <c r="B392" t="n">
@@ -4845,7 +4843,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="3" t="n">
         <v>46050</v>
       </c>
       <c r="B393" t="n">
@@ -4853,7 +4851,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="3" t="n">
         <v>46051</v>
       </c>
       <c r="B394" t="n">
@@ -4861,7 +4859,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="3" t="n">
         <v>46052</v>
       </c>
       <c r="B395" t="n">
@@ -4869,7 +4867,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="3" t="n">
         <v>46053</v>
       </c>
       <c r="B396" t="n">
@@ -4877,7 +4875,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B397" t="n">
@@ -4885,7 +4883,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="3" t="n">
         <v>46055</v>
       </c>
       <c r="B398" t="n">
@@ -4893,7 +4891,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="3" t="n">
         <v>46056</v>
       </c>
       <c r="B399" t="n">
@@ -4901,7 +4899,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="B400" t="n">
@@ -4909,7 +4907,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="3" t="n">
         <v>46058</v>
       </c>
       <c r="B401" t="n">
@@ -4917,7 +4915,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="3" t="n">
         <v>46059</v>
       </c>
       <c r="B402" t="n">
@@ -4925,7 +4923,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="3" t="n">
         <v>46060</v>
       </c>
       <c r="B403" t="n">
@@ -4933,7 +4931,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="3" t="n">
         <v>46061</v>
       </c>
       <c r="B404" t="n">
@@ -4941,7 +4939,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B405" t="n">
@@ -4949,7 +4947,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="B406" t="n">
@@ -4957,7 +4955,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="3" t="n">
         <v>46064</v>
       </c>
       <c r="B407" t="n">
@@ -4965,7 +4963,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="B408" t="n">
@@ -4973,7 +4971,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="3" t="n">
         <v>46066</v>
       </c>
       <c r="B409" t="n">
@@ -4981,7 +4979,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="3" t="n">
         <v>46067</v>
       </c>
       <c r="B410" t="n">
@@ -4989,7 +4987,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="3" t="n">
         <v>46068</v>
       </c>
       <c r="B411" t="n">
@@ -4997,7 +4995,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="3" t="n">
         <v>46069</v>
       </c>
       <c r="B412" t="n">
@@ -5005,7 +5003,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="3" t="n">
         <v>46070</v>
       </c>
       <c r="B413" t="n">
@@ -5013,7 +5011,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="3" t="n">
         <v>46071</v>
       </c>
       <c r="B414" t="n">
@@ -5021,7 +5019,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="3" t="n">
         <v>46072</v>
       </c>
       <c r="B415" t="n">
@@ -5029,7 +5027,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="3" t="n">
         <v>46073</v>
       </c>
       <c r="B416" t="n">
@@ -5037,7 +5035,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="3" t="n">
         <v>46074</v>
       </c>
       <c r="B417" t="n">
@@ -5045,7 +5043,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="3" t="n">
         <v>46075</v>
       </c>
       <c r="B418" t="n">
@@ -5053,7 +5051,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="3" t="n">
         <v>46076</v>
       </c>
       <c r="B419" t="n">
@@ -5061,7 +5059,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="3" t="n">
         <v>46077</v>
       </c>
       <c r="B420" t="n">
@@ -5069,7 +5067,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="3" t="n">
         <v>46078</v>
       </c>
       <c r="B421" t="n">
@@ -5077,7 +5075,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="3" t="n">
         <v>46079</v>
       </c>
       <c r="B422" t="n">
@@ -5085,7 +5083,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="3" t="n">
         <v>46080</v>
       </c>
       <c r="B423" t="n">
@@ -5093,7 +5091,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="3" t="n">
         <v>46081</v>
       </c>
       <c r="B424" t="n">
@@ -5101,7 +5099,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B425" t="n">
@@ -5114,7 +5112,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="3" t="n">
         <v>46083</v>
       </c>
       <c r="B426" t="n">
@@ -5122,7 +5120,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="3" t="n">
         <v>46084</v>
       </c>
       <c r="B427" t="n">
@@ -5130,7 +5128,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="3" t="n">
         <v>46085</v>
       </c>
       <c r="B428" t="n">
@@ -5138,7 +5136,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="3" t="n">
         <v>46086</v>
       </c>
       <c r="B429" t="n">
@@ -5146,7 +5144,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="3" t="n">
         <v>46087</v>
       </c>
       <c r="B430" t="n">
@@ -5154,7 +5152,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="3" t="n">
         <v>46088</v>
       </c>
       <c r="B431" t="n">
@@ -5162,7 +5160,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="3" t="n">
         <v>46089</v>
       </c>
       <c r="B432" t="n">
@@ -5170,7 +5168,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="3" t="n">
         <v>46090</v>
       </c>
       <c r="B433" t="n">
@@ -5178,7 +5176,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="B434" t="n">
@@ -5186,7 +5184,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="3" t="n">
         <v>46092</v>
       </c>
       <c r="B435" t="n">
@@ -5194,7 +5192,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="3" t="n">
         <v>46093</v>
       </c>
       <c r="B436" t="n">
@@ -5202,7 +5200,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="3" t="n">
         <v>46094</v>
       </c>
       <c r="B437" t="n">
@@ -5210,7 +5208,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="3" t="n">
         <v>46095</v>
       </c>
       <c r="B438" t="n">
@@ -5218,7 +5216,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="3" t="n">
         <v>46096</v>
       </c>
       <c r="B439" t="n">
@@ -5226,7 +5224,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="3" t="n">
         <v>46097</v>
       </c>
       <c r="B440" t="n">
@@ -5234,7 +5232,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B441" t="n">
@@ -5242,7 +5240,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B442" t="n">
@@ -5250,7 +5248,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B443" t="n">
@@ -5258,7 +5256,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B444" t="n">
@@ -5266,7 +5264,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B445" t="n">
@@ -5274,7 +5272,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B446" t="n">
@@ -5282,7 +5280,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B447" t="n">
@@ -5290,7 +5288,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B448" t="n">
@@ -5298,7 +5296,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B449" t="n">
@@ -5306,7 +5304,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B450" t="n">
@@ -5314,7 +5312,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B451" t="n">
@@ -5322,7 +5320,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B452" t="n">
@@ -5330,7 +5328,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B453" t="n">
@@ -5338,7 +5336,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B454" t="n">
@@ -5346,7 +5344,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B455" t="n">
@@ -5354,7 +5352,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B456" t="n">
@@ -5362,7 +5360,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B457" t="n">
@@ -5370,7 +5368,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B458" t="n">
@@ -5378,7 +5376,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B459" t="n">
@@ -5386,7 +5384,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B460" t="n">
@@ -5394,7 +5392,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B461" t="n">
@@ -5402,7 +5400,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B462" t="n">
@@ -5410,7 +5408,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B463" t="n">
@@ -5418,7 +5416,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B464" t="n">
@@ -5426,7 +5424,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B465" t="n">
@@ -5434,7 +5432,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B466" t="n">
@@ -5442,7 +5440,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B467" t="n">
@@ -5450,7 +5448,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B468" t="n">
@@ -5458,7 +5456,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B469" t="n">
@@ -5466,7 +5464,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B470" t="n">
@@ -5474,7 +5472,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B471" t="n">
@@ -5482,7 +5480,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B472" t="n">
@@ -5490,7 +5488,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="3" t="n">
         <v>46130</v>
       </c>
       <c r="B473" t="n">
@@ -5498,7 +5496,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="3" t="n">
         <v>46131</v>
       </c>
       <c r="B474" t="n">
@@ -5506,7 +5504,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="3" t="n">
         <v>46132</v>
       </c>
       <c r="B475" t="n">
@@ -5514,7 +5512,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="3" t="n">
         <v>46133</v>
       </c>
       <c r="B476" t="n">
@@ -5522,7 +5520,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="3" t="n">
         <v>46134</v>
       </c>
       <c r="B477" t="n">
@@ -5530,7 +5528,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="3" t="n">
         <v>46135</v>
       </c>
       <c r="B478" t="n">
@@ -5538,7 +5536,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="3" t="n">
         <v>46136</v>
       </c>
       <c r="B479" t="n">
@@ -5546,7 +5544,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="3" t="n">
         <v>46137</v>
       </c>
       <c r="B480" t="n">
@@ -5554,7 +5552,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="3" t="n">
         <v>46138</v>
       </c>
       <c r="B481" t="n">
@@ -5562,7 +5560,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="3" t="n">
         <v>46139</v>
       </c>
       <c r="B482" t="n">
@@ -5570,7 +5568,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="3" t="n">
         <v>46140</v>
       </c>
       <c r="B483" t="n">
@@ -5578,7 +5576,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="3" t="n">
         <v>46141</v>
       </c>
       <c r="B484" t="n">
@@ -5586,7 +5584,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="3" t="n">
         <v>46142</v>
       </c>
       <c r="B485" t="n">
@@ -5594,7 +5592,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B486" t="n">
@@ -5607,7 +5605,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="3" t="n">
         <v>46144</v>
       </c>
       <c r="B487" t="n">
@@ -5615,7 +5613,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="3" t="n">
         <v>46145</v>
       </c>
       <c r="B488" t="n">
@@ -5623,7 +5621,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="3" t="n">
         <v>46146</v>
       </c>
       <c r="B489" t="n">
@@ -5631,7 +5629,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="3" t="n">
         <v>46147</v>
       </c>
       <c r="B490" t="n">
@@ -5639,7 +5637,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="3" t="n">
         <v>46148</v>
       </c>
       <c r="B491" t="n">
@@ -5647,7 +5645,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="3" t="n">
         <v>46149</v>
       </c>
       <c r="B492" t="n">
@@ -5655,7 +5653,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="3" t="n">
         <v>46150</v>
       </c>
       <c r="B493" t="n">
@@ -5663,7 +5661,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="3" t="n">
         <v>46151</v>
       </c>
       <c r="B494" t="n">
@@ -5671,7 +5669,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="3" t="n">
         <v>46152</v>
       </c>
       <c r="B495" t="n">
@@ -5679,7 +5677,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="3" t="n">
         <v>46153</v>
       </c>
       <c r="B496" t="n">
@@ -5687,7 +5685,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="3" t="n">
         <v>46154</v>
       </c>
       <c r="B497" t="n">
@@ -5695,7 +5693,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="3" t="n">
         <v>46155</v>
       </c>
       <c r="B498" t="n">
@@ -5703,7 +5701,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="3" t="n">
         <v>46156</v>
       </c>
       <c r="B499" t="n">
@@ -5711,7 +5709,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="3" t="n">
         <v>46157</v>
       </c>
       <c r="B500" t="n">
@@ -5719,7 +5717,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="3" t="n">
         <v>46158</v>
       </c>
       <c r="B501" t="n">
@@ -5727,7 +5725,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="3" t="n">
         <v>46159</v>
       </c>
       <c r="B502" t="n">
@@ -5735,7 +5733,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="3" t="n">
         <v>46160</v>
       </c>
       <c r="B503" t="n">
@@ -5743,7 +5741,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="3" t="n">
         <v>46161</v>
       </c>
       <c r="B504" t="n">
@@ -5751,7 +5749,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="3" t="n">
         <v>46162</v>
       </c>
       <c r="B505" t="n">
@@ -5759,7 +5757,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="3" t="n">
         <v>46163</v>
       </c>
       <c r="B506" t="n">
@@ -5767,7 +5765,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="3" t="n">
         <v>46164</v>
       </c>
       <c r="B507" t="n">
@@ -5775,7 +5773,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="3" t="n">
         <v>46165</v>
       </c>
       <c r="B508" t="n">
@@ -5783,7 +5781,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="3" t="n">
         <v>46166</v>
       </c>
       <c r="B509" t="n">
@@ -5791,7 +5789,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="3" t="n">
         <v>46167</v>
       </c>
       <c r="B510" t="n">
@@ -5799,7 +5797,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="3" t="n">
         <v>46168</v>
       </c>
       <c r="B511" t="n">
@@ -5807,7 +5805,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="3" t="n">
         <v>46169</v>
       </c>
       <c r="B512" t="n">
@@ -5815,7 +5813,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="3" t="n">
         <v>46170</v>
       </c>
       <c r="B513" t="n">
@@ -5823,7 +5821,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B514" t="n">
@@ -5831,7 +5829,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="3" t="n">
         <v>46172</v>
       </c>
       <c r="B515" t="n">
@@ -5839,7 +5837,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="3" t="n">
         <v>46173</v>
       </c>
       <c r="B516" t="n">
@@ -5847,7 +5845,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B517" t="n">
@@ -5855,7 +5853,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="3" t="n">
         <v>46175</v>
       </c>
       <c r="B518" t="n">
@@ -5863,7 +5861,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="3" t="n">
         <v>46176</v>
       </c>
       <c r="B519" t="n">
@@ -5871,7 +5869,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="3" t="n">
         <v>46177</v>
       </c>
       <c r="B520" t="n">
@@ -5879,7 +5877,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="3" t="n">
         <v>46178</v>
       </c>
       <c r="B521" t="n">
@@ -5887,7 +5885,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="3" t="n">
         <v>46179</v>
       </c>
       <c r="B522" t="n">
@@ -5895,7 +5893,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="3" t="n">
         <v>46180</v>
       </c>
       <c r="B523" t="n">
@@ -5903,7 +5901,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="3" t="n">
         <v>46181</v>
       </c>
       <c r="B524" t="n">
@@ -5911,7 +5909,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="3" t="n">
         <v>46183</v>
       </c>
       <c r="B525" t="n">
@@ -5919,7 +5917,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="3" t="n">
         <v>46184</v>
       </c>
       <c r="B526" t="n">
@@ -5927,7 +5925,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="3" t="n">
         <v>46185</v>
       </c>
       <c r="B527" t="n">
@@ -5935,7 +5933,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="3" t="n">
         <v>46186</v>
       </c>
       <c r="B528" t="n">
@@ -5943,7 +5941,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="3" t="n">
         <v>46187</v>
       </c>
       <c r="B529" t="n">
@@ -5951,7 +5949,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="3" t="n">
         <v>46188</v>
       </c>
       <c r="B530" t="n">
@@ -5959,7 +5957,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="3" t="n">
         <v>46189</v>
       </c>
       <c r="B531" t="n">
@@ -5967,7 +5965,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="3" t="n">
         <v>46190</v>
       </c>
       <c r="B532" t="n">
@@ -5975,7 +5973,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="3" t="n">
         <v>46191</v>
       </c>
       <c r="B533" t="n">
@@ -5983,7 +5981,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="3" t="n">
         <v>46192</v>
       </c>
       <c r="B534" t="n">
@@ -5991,7 +5989,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="3" t="n">
         <v>46193</v>
       </c>
       <c r="B535" t="n">
@@ -5999,7 +5997,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="3" t="n">
         <v>46194</v>
       </c>
       <c r="B536" t="n">
@@ -6007,7 +6005,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="B537" t="n">
@@ -6015,7 +6013,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="3" t="n">
         <v>46196</v>
       </c>
       <c r="B538" t="n">
@@ -6023,7 +6021,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="3" t="n">
         <v>46197</v>
       </c>
       <c r="B539" t="n">
@@ -6031,7 +6029,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="3" t="n">
         <v>46198</v>
       </c>
       <c r="B540" t="n">
@@ -6039,7 +6037,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="3" t="n">
         <v>46199</v>
       </c>
       <c r="B541" t="n">
@@ -6047,7 +6045,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="3" t="n">
         <v>46200</v>
       </c>
       <c r="B542" t="n">
@@ -6055,7 +6053,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="3" t="n">
         <v>46201</v>
       </c>
       <c r="B543" t="n">
@@ -6063,7 +6061,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="3" t="n">
         <v>46202</v>
       </c>
       <c r="B544" t="n">
@@ -6071,7 +6069,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B545" t="n">
@@ -6079,7 +6077,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B546" t="n">
@@ -6092,7 +6090,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="B547" t="n">
@@ -6100,7 +6098,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="3" t="n">
         <v>46206</v>
       </c>
       <c r="B548" t="n">
@@ -6108,7 +6106,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="3" t="n">
         <v>46207</v>
       </c>
       <c r="B549" t="n">
@@ -6116,7 +6114,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="3" t="n">
         <v>46208</v>
       </c>
       <c r="B550" t="n">
@@ -6124,7 +6122,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="B551" t="n">
@@ -6132,7 +6130,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="B552" t="n">
@@ -6140,7 +6138,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="B553" t="n">
@@ -6148,7 +6146,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="B554" t="n">
@@ -6156,7 +6154,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="3" t="n">
         <v>46213</v>
       </c>
       <c r="B555" t="n">
@@ -6164,7 +6162,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="B556" t="n">
@@ -6172,7 +6170,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="3" t="n">
         <v>46215</v>
       </c>
       <c r="B557" t="n">
@@ -6180,7 +6178,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="3" t="n">
         <v>46216</v>
       </c>
       <c r="B558" t="n">
@@ -6188,7 +6186,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="B559" t="n">
@@ -6196,7 +6194,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="B560" t="n">
@@ -6204,7 +6202,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="B561" t="n">
@@ -6212,7 +6210,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="3" t="n">
         <v>46220</v>
       </c>
       <c r="B562" t="n">
@@ -6220,7 +6218,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="3" t="n">
         <v>46221</v>
       </c>
       <c r="B563" t="n">
@@ -6228,7 +6226,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="3" t="n">
         <v>46222</v>
       </c>
       <c r="B564" t="n">
@@ -6236,7 +6234,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="B565" t="n">
@@ -6244,7 +6242,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B566" t="n">
@@ -6252,7 +6250,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="B567" t="n">
@@ -6260,7 +6258,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="3" t="n">
         <v>46226</v>
       </c>
       <c r="B568" t="n">
@@ -6268,7 +6266,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B569" t="n">
@@ -6276,7 +6274,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="B570" t="n">
@@ -6284,7 +6282,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="3" t="n">
         <v>46229</v>
       </c>
       <c r="B571" t="n">
@@ -6292,7 +6290,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="3" t="n">
         <v>46230</v>
       </c>
       <c r="B572" t="n">
@@ -6300,7 +6298,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="B573" t="n">
@@ -6308,7 +6306,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B574" t="n">
@@ -6316,7 +6314,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="B575" t="n">
@@ -6324,7 +6322,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="B576" t="n">
@@ -6332,7 +6330,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B577" t="n">
@@ -6340,7 +6338,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="B578" t="n">
@@ -6348,7 +6346,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="B579" t="n">
@@ -6356,7 +6354,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="B580" t="n">
@@ -6364,7 +6362,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="B581" t="n">
@@ -6372,7 +6370,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="B582" t="n">
@@ -6380,7 +6378,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="3" t="n">
         <v>46241</v>
       </c>
       <c r="B583" t="n">
@@ -6388,7 +6386,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="3" t="n">
         <v>46242</v>
       </c>
       <c r="B584" t="n">
@@ -6396,7 +6394,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="3" t="n">
         <v>46243</v>
       </c>
       <c r="B585" t="n">
@@ -6404,7 +6402,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="B586" t="n">
@@ -6412,7 +6410,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="B587" t="n">
@@ -6420,7 +6418,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="B588" t="n">
@@ -6428,7 +6426,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="B589" t="n">
@@ -6436,7 +6434,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="3" t="n">
         <v>46248</v>
       </c>
       <c r="B590" t="n">
@@ -6444,7 +6442,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="3" t="n">
         <v>46249</v>
       </c>
       <c r="B591" t="n">
@@ -6452,7 +6450,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="3" t="n">
         <v>46250</v>
       </c>
       <c r="B592" t="n">
@@ -6460,7 +6458,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="B593" t="n">
@@ -6468,7 +6466,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="B594" t="n">
@@ -6476,7 +6474,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B595" t="n">
@@ -6484,7 +6482,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="B596" t="n">
@@ -6492,7 +6490,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="3" t="n">
         <v>46255</v>
       </c>
       <c r="B597" t="n">
@@ -6500,7 +6498,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="3" t="n">
         <v>46256</v>
       </c>
       <c r="B598" t="n">
@@ -6508,7 +6506,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="3" t="n">
         <v>46257</v>
       </c>
       <c r="B599" t="n">
@@ -6516,7 +6514,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="3" t="n">
         <v>46258</v>
       </c>
       <c r="B600" t="n">
@@ -6524,7 +6522,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="3" t="n">
         <v>46259</v>
       </c>
       <c r="B601" t="n">
@@ -6532,7 +6530,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="3" t="n">
         <v>46260</v>
       </c>
       <c r="B602" t="n">
@@ -6540,7 +6538,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="2" t="n">
+      <c r="A603" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="B603" t="n">
@@ -6548,7 +6546,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="2" t="n">
+      <c r="A604" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B604" t="n">
@@ -6556,7 +6554,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="2" t="n">
+      <c r="A605" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="B605" t="n">
@@ -6564,7 +6562,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="2" t="n">
+      <c r="A606" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="B606" t="n">
@@ -6572,7 +6570,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="2" t="n">
+      <c r="A607" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="B607" t="n">
@@ -6580,7 +6578,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="2" t="n">
+      <c r="A608" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B608" t="n">
@@ -6593,7 +6591,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="2" t="n">
+      <c r="A609" s="3" t="n">
         <v>46267</v>
       </c>
       <c r="B609" t="n">
@@ -6601,7 +6599,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="2" t="n">
+      <c r="A610" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="B610" t="n">
@@ -6609,7 +6607,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="2" t="n">
+      <c r="A611" s="3" t="n">
         <v>46269</v>
       </c>
       <c r="B611" t="n">
@@ -6617,7 +6615,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="2" t="n">
+      <c r="A612" s="3" t="n">
         <v>46270</v>
       </c>
       <c r="B612" t="n">
@@ -6625,7 +6623,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="2" t="n">
+      <c r="A613" s="3" t="n">
         <v>46271</v>
       </c>
       <c r="B613" t="n">
@@ -6633,7 +6631,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="2" t="n">
+      <c r="A614" s="3" t="n">
         <v>46272</v>
       </c>
       <c r="B614" t="n">
@@ -6641,7 +6639,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="2" t="n">
+      <c r="A615" s="3" t="n">
         <v>46273</v>
       </c>
       <c r="B615" t="n">
@@ -6649,7 +6647,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="2" t="n">
+      <c r="A616" s="3" t="n">
         <v>46274</v>
       </c>
       <c r="B616" t="n">
@@ -6657,7 +6655,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="2" t="n">
+      <c r="A617" s="3" t="n">
         <v>46275</v>
       </c>
       <c r="B617" t="n">
@@ -6665,7 +6663,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="2" t="n">
+      <c r="A618" s="3" t="n">
         <v>46276</v>
       </c>
       <c r="B618" t="n">
@@ -6673,7 +6671,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="2" t="n">
+      <c r="A619" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="B619" t="n">
@@ -6681,7 +6679,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="2" t="n">
+      <c r="A620" s="3" t="n">
         <v>46278</v>
       </c>
       <c r="B620" t="n">
@@ -6689,7 +6687,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="2" t="n">
+      <c r="A621" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="B621" t="n">
@@ -6697,7 +6695,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="2" t="n">
+      <c r="A622" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="B622" t="n">
@@ -6705,7 +6703,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="2" t="n">
+      <c r="A623" s="3" t="n">
         <v>46281</v>
       </c>
       <c r="B623" t="n">
@@ -6713,7 +6711,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="2" t="n">
+      <c r="A624" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="B624" t="n">
@@ -6721,7 +6719,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="2" t="n">
+      <c r="A625" s="3" t="n">
         <v>46283</v>
       </c>
       <c r="B625" t="n">
@@ -6729,7 +6727,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="2" t="n">
+      <c r="A626" s="3" t="n">
         <v>46284</v>
       </c>
       <c r="B626" t="n">
@@ -6737,7 +6735,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="2" t="n">
+      <c r="A627" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="B627" t="n">
@@ -6745,7 +6743,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="2" t="n">
+      <c r="A628" s="3" t="n">
         <v>46286</v>
       </c>
       <c r="B628" t="n">
@@ -6753,7 +6751,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="2" t="n">
+      <c r="A629" s="3" t="n">
         <v>46287</v>
       </c>
       <c r="B629" t="n">
@@ -6761,7 +6759,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="2" t="n">
+      <c r="A630" s="3" t="n">
         <v>46288</v>
       </c>
       <c r="B630" t="n">
@@ -6769,7 +6767,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="2" t="n">
+      <c r="A631" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="B631" t="n">
@@ -6777,7 +6775,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="2" t="n">
+      <c r="A632" s="3" t="n">
         <v>46290</v>
       </c>
       <c r="B632" t="n">
@@ -6785,7 +6783,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="2" t="n">
+      <c r="A633" s="3" t="n">
         <v>46291</v>
       </c>
       <c r="B633" t="n">
@@ -6793,7 +6791,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="2" t="n">
+      <c r="A634" s="3" t="n">
         <v>46292</v>
       </c>
       <c r="B634" t="n">
@@ -6801,7 +6799,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="2" t="n">
+      <c r="A635" s="3" t="n">
         <v>46293</v>
       </c>
       <c r="B635" t="n">
@@ -6809,7 +6807,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="2" t="n">
+      <c r="A636" s="3" t="n">
         <v>46294</v>
       </c>
       <c r="B636" t="n">
@@ -6817,7 +6815,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="2" t="n">
+      <c r="A637" s="3" t="n">
         <v>46295</v>
       </c>
       <c r="B637" t="n">
@@ -6825,7 +6823,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="2" t="n">
+      <c r="A638" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B638" t="n">
@@ -6863,7 +6861,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -6871,7 +6869,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -6879,7 +6877,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -6887,7 +6885,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -6895,7 +6893,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -6903,7 +6901,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -6911,7 +6909,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -6919,7 +6917,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -6927,7 +6925,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -6935,7 +6933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -6943,7 +6941,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -6951,7 +6949,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -6959,7 +6957,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -6967,7 +6965,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -6975,7 +6973,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -6983,7 +6981,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -6991,7 +6989,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -6999,7 +6997,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -7007,7 +7005,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -7015,7 +7013,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -7023,7 +7021,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -7031,7 +7029,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -7039,7 +7037,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -7047,7 +7045,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -7055,7 +7053,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -7063,7 +7061,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -7071,7 +7069,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -7079,7 +7077,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -7087,7 +7085,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -7095,7 +7093,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -7103,7 +7101,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -7111,7 +7109,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -7119,7 +7117,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -7127,7 +7125,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -7135,7 +7133,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -7143,7 +7141,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -7151,7 +7149,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -7159,7 +7157,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -7167,7 +7165,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -7175,7 +7173,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -7183,7 +7181,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -7191,7 +7189,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -7199,7 +7197,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -7207,7 +7205,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -7215,7 +7213,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -7223,7 +7221,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -7231,7 +7229,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -7239,7 +7237,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -7247,7 +7245,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -7255,7 +7253,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -7263,7 +7261,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -7271,7 +7269,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -7279,7 +7277,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -7287,7 +7285,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -7295,7 +7293,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -7303,7 +7301,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -7311,7 +7309,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -7319,7 +7317,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -7327,7 +7325,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -7335,7 +7333,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -7343,7 +7341,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -7351,7 +7349,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -7359,7 +7357,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -7367,7 +7365,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -7375,7 +7373,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -7383,7 +7381,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -7391,7 +7389,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -7399,7 +7397,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -7407,7 +7405,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -7415,7 +7413,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B71" t="n">
